--- a/artfynd/S 740-2025 artfynd.xlsx
+++ b/artfynd/S 740-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4251153</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,8 +882,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111962970</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 740-2025 artfynd.xlsx
+++ b/artfynd/S 740-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4251153</v>
+        <v>135866066</v>
       </c>
       <c r="B2" t="n">
-        <v>97986</v>
+        <v>106286</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>221154</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Skogsstjärna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lysimachia europaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) U. Manns &amp; Anderb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjärfinnberget, 875 m SSO topplatån, Vrm</t>
+          <t>Hållibravägen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428768</v>
+        <v>418981</v>
       </c>
       <c r="R2" t="n">
-        <v>6674202</v>
+        <v>6688799</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-08-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-08-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,77 +763,76 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vändplan i hedbarrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Crister Albinsson</t>
+          <t>Jan Teodorsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Crister Albinsson, Jan Teodorsson, Per Larsson</t>
+          <t>Jan Teodorsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4251153</t>
+          <t>https://artportalen.se/Sighting/135866066</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111962970</v>
+        <v>135866069</v>
       </c>
       <c r="B3" t="n">
-        <v>97993</v>
+        <v>107782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221940</v>
+        <v>221705</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mellanlummer</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium zeilleri</t>
+          <t>Melampyrum pratense</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Rouy) Greuter &amp; Burdet</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dordimossen, Vrm</t>
+          <t>Hållibravägen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422940</v>
+        <v>418981</v>
       </c>
       <c r="R3" t="n">
-        <v>6670783</v>
+        <v>6688799</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,36 +856,354 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anaelle Stenman</t>
+          <t>Jan Teodorsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anaelle Stenman</t>
+          <t>Jan Teodorsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135866069</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135866032</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98136</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hållibravägen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>418981</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6688799</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jan Teodorsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jan Teodorsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135866032</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4251153</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tjärfinnberget, 875 m SSO topplatån, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>428768</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6674202</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2012-08-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2012-08-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vändplan i hedbarrskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Crister Albinsson, Jan Teodorsson, Per Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4251153</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>111962970</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97993</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221940</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mellanlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium zeilleri</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Rouy) Greuter &amp; Burdet</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dordimossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>422940</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6670783</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anaelle Stenman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anaelle Stenman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/111962970</t>
         </is>
@@ -892,6 +1213,9 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 740-2025 artfynd.xlsx
+++ b/artfynd/S 740-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135866066</v>
       </c>
       <c r="B2" t="n">
-        <v>106286</v>
+        <v>106288</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135866069</v>
       </c>
       <c r="B3" t="n">
-        <v>107782</v>
+        <v>107784</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135866032</v>
       </c>
       <c r="B4" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 740-2025 artfynd.xlsx
+++ b/artfynd/S 740-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135866066</v>
       </c>
       <c r="B2" t="n">
-        <v>106288</v>
+        <v>106308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135866069</v>
       </c>
       <c r="B3" t="n">
-        <v>107784</v>
+        <v>107807</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135866032</v>
       </c>
       <c r="B4" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 740-2025 artfynd.xlsx
+++ b/artfynd/S 740-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135866066</v>
       </c>
       <c r="B2" t="n">
-        <v>106308</v>
+        <v>106310</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135866069</v>
       </c>
       <c r="B3" t="n">
-        <v>107807</v>
+        <v>107809</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135866032</v>
       </c>
       <c r="B4" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 740-2025 artfynd.xlsx
+++ b/artfynd/S 740-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135866066</v>
       </c>
       <c r="B2" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135866069</v>
       </c>
       <c r="B3" t="n">
-        <v>107809</v>
+        <v>107810</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135866032</v>
       </c>
       <c r="B4" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 740-2025 artfynd.xlsx
+++ b/artfynd/S 740-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135866066</v>
       </c>
       <c r="B2" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135866069</v>
       </c>
       <c r="B3" t="n">
-        <v>107810</v>
+        <v>107811</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135866032</v>
       </c>
       <c r="B4" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 740-2025 artfynd.xlsx
+++ b/artfynd/S 740-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135866066</v>
       </c>
       <c r="B2" t="n">
-        <v>106312</v>
+        <v>106318</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135866069</v>
       </c>
       <c r="B3" t="n">
-        <v>107811</v>
+        <v>107817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135866032</v>
       </c>
       <c r="B4" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 740-2025 artfynd.xlsx
+++ b/artfynd/S 740-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135866066</v>
       </c>
       <c r="B2" t="n">
-        <v>106318</v>
+        <v>106319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135866069</v>
       </c>
       <c r="B3" t="n">
-        <v>107817</v>
+        <v>107818</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135866032</v>
       </c>
       <c r="B4" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 740-2025 artfynd.xlsx
+++ b/artfynd/S 740-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135866066</v>
       </c>
       <c r="B2" t="n">
-        <v>106319</v>
+        <v>106330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135866069</v>
       </c>
       <c r="B3" t="n">
-        <v>107818</v>
+        <v>107829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135866032</v>
       </c>
       <c r="B4" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 740-2025 artfynd.xlsx
+++ b/artfynd/S 740-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135866066</v>
       </c>
       <c r="B2" t="n">
-        <v>106330</v>
+        <v>106343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135866069</v>
       </c>
       <c r="B3" t="n">
-        <v>107829</v>
+        <v>107842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135866032</v>
       </c>
       <c r="B4" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 740-2025 artfynd.xlsx
+++ b/artfynd/S 740-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135866066</v>
       </c>
       <c r="B2" t="n">
-        <v>106343</v>
+        <v>106344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135866069</v>
       </c>
       <c r="B3" t="n">
-        <v>107842</v>
+        <v>107843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135866032</v>
       </c>
       <c r="B4" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 740-2025 artfynd.xlsx
+++ b/artfynd/S 740-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135866066</v>
       </c>
       <c r="B2" t="n">
-        <v>106344</v>
+        <v>106357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135866069</v>
       </c>
       <c r="B3" t="n">
-        <v>107843</v>
+        <v>107856</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135866032</v>
       </c>
       <c r="B4" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 740-2025 artfynd.xlsx
+++ b/artfynd/S 740-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135866066</v>
       </c>
       <c r="B2" t="n">
-        <v>106357</v>
+        <v>106358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135866069</v>
       </c>
       <c r="B3" t="n">
-        <v>107856</v>
+        <v>107857</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135866032</v>
       </c>
       <c r="B4" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
